--- a/out/LSTM-mamba2_repeat_1_000007.xlsx
+++ b/out/LSTM-mamba2_repeat_1_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.3</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.166666627777778</v>
+        <v>-0.3</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>2.166666627777778</v>
+        <v>-0.3</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>2.166666627777778</v>
+        <v>-0.3</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.166666627777778</v>
+        <v>-0.3</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>2.166666627777778</v>
+        <v>-0.3</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>2.166666627777778</v>
+        <v>-0.3</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>2.166666627777778</v>
+        <v>-0.3</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.166666627777778</v>
+        <v>-0.3</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.3</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.3</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.3</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.3</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.3</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.3</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.3</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.3</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.3</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.3</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.3</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.3</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.3</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.3</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.3</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.3</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.3</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.3</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.3</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.3</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.3</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,17 +31942,17 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC39" t="n">
-        <v>0</v>
+        <v>-7.712256331345998e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,21 +32733,21 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0</v>
+        <v>0.889109252280405</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA40" t="n">
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC40" t="n">
-        <v>-6.544820638163947e-05</v>
+        <v>1.779592907008404</v>
       </c>
     </row>
     <row r="41">
@@ -33528,21 +33528,21 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>-0.08439480559912851</v>
+        <v>0.1333258984963202</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC41" t="n">
-        <v>-0.08446025380551012</v>
+        <v>1.155942144807108</v>
       </c>
     </row>
     <row r="42">
@@ -34323,21 +34323,21 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0</v>
+        <v>0.1667007545622656</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA42" t="n">
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC42" t="n">
-        <v>-0.0845195349753116</v>
+        <v>1.356038928517799</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.09896576060908549</v>
+        <v>0.2389645784281521</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC43" t="n">
-        <v>0.1136497132289545</v>
+        <v>1.667361733030028</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.136155436148725</v>
+        <v>0.2556451129256772</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.2870067489827375</v>
+        <v>1.939704871897068</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.1591724543333937</v>
+        <v>0.2709315542955592</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.4692093156517008</v>
+        <v>2.225943688836998</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.07118428547290268</v>
+        <v>0.1222670373213373</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.4522619758627245</v>
+        <v>2.19931958941948</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.03426610669047592</v>
+        <v>0.05904874746033055</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.4495476573862869</v>
+        <v>2.19505546025556</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.01624806723683932</v>
+        <v>0.02813558306727647</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.4477489483733648</v>
+        <v>2.192229698691393</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.004472507594134571</v>
+        <v>0.008333563627179606</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.4404296968309218</v>
+        <v>2.180734450292196</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.003091197288664339</v>
+        <v>0.005510641582937633</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.4421367540823403</v>
+        <v>2.18341892269172</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.001584137874602457</v>
+        <v>0.002817967231921131</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.4422126150571173</v>
+        <v>2.183540957973626</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0008103004465842412</v>
+        <v>0.001439560167255453</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.4422480320039561</v>
+        <v>2.183599447234295</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0002889485289411763</v>
+        <v>0.0005376864856202011</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.442014038558902</v>
+        <v>2.183234922977324</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0001571842594622037</v>
+        <v>0.0002911771458358382</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.4420399776976137</v>
+        <v>2.183278531161338</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>7.264066268727065e-05</v>
+        <v>0.0001372566611499408</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.4420279255102805</v>
+        <v>2.183262475273386</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>4.460616585560791e-05</v>
+        <v>8.355596056915365e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.4420446442666803</v>
+        <v>2.183291468911106</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>2.155523189501682e-05</v>
+        <v>4.132161208684532e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.4420422451232253</v>
+        <v>2.183290504722986</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>7.395902747928427e-06</v>
+        <v>1.698004887727391e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.4420363490378794</v>
+        <v>2.183284113910244</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>3.158324102806951e-06</v>
+        <v>9.070610155389825e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.4420355440154751</v>
+        <v>2.1832855457952</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-7.922409131858519e-07</v>
+        <v>1.993667665820105e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.4420296289786946</v>
+        <v>2.18327917324003</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.168604696895391e-06</v>
+        <v>-1.911892527543644e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.4420240808504736</v>
+        <v>2.183273351047698</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.001043275021943e-06</v>
+        <v>-3.887371769088796e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4420192462161551</v>
+        <v>2.183268599772485</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0</v>
+        <v>-4.031182895915095e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4420191022322476</v>
+        <v>2.183263310624922</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4420190794979462</v>
+        <v>2.183263287890621</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.442019397778163</v>
+        <v>2.183263606170838</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4420204890246198</v>
+        <v>2.183264697417295</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4420197994174839</v>
+        <v>2.183264007810159</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4420198297298856</v>
+        <v>2.183264038122561</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4420196402773754</v>
+        <v>2.18326384867005</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4420196933240784</v>
+        <v>2.183263901716753</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4420197463707812</v>
+        <v>2.183263954763456</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4420197084802792</v>
+        <v>2.183263916872954</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4420195796525725</v>
+        <v>2.183263788045247</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.442019435668665</v>
+        <v>2.18326364406134</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4420192765285566</v>
+        <v>2.183263484921231</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4420193295752595</v>
+        <v>2.183263537967934</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4420192765285566</v>
+        <v>2.183263484921231</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4420192765285566</v>
+        <v>2.183263484921231</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4420190946541471</v>
+        <v>2.183263303046822</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4420192613723558</v>
+        <v>2.183263469765031</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4420194584029661</v>
+        <v>2.183263666795641</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4420192992628578</v>
+        <v>2.183263507655533</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4420193371533598</v>
+        <v>2.183263545546035</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4420195341839699</v>
+        <v>2.183263742576645</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4420195114496688</v>
+        <v>2.183263719842344</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4420193598876609</v>
+        <v>2.183263568280336</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4420192841066569</v>
+        <v>2.183263492499332</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4420193826219621</v>
+        <v>2.183263591014637</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4420193902000624</v>
+        <v>2.183263598592738</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4420196554335763</v>
+        <v>2.183263863826252</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4420193598876609</v>
+        <v>2.183263568280336</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4420196023868737</v>
+        <v>2.183263810779549</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4420196857459781</v>
+        <v>2.183263894138653</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4420195190277693</v>
+        <v>2.183263727420444</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4420197084802792</v>
+        <v>2.183263916872954</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4420193598876609</v>
+        <v>2.183263568280336</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4420191552789502</v>
+        <v>2.183263363671625</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4420192689504563</v>
+        <v>2.183263477343131</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4420192841066569</v>
+        <v>2.183263492499332</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4420190491855447</v>
+        <v>2.18326325757822</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4420191098103479</v>
+        <v>2.183263318203023</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4420189809826412</v>
+        <v>2.183263189375316</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4420191173884482</v>
+        <v>2.183263325781123</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4420192916847575</v>
+        <v>2.183263500077433</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.442019435668665</v>
+        <v>2.18326364406134</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4420192689504563</v>
+        <v>2.183263477343131</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4420192613723558</v>
+        <v>2.183263469765031</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4420189734045407</v>
+        <v>2.183263181797216</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4420189885607415</v>
+        <v>2.183263196953417</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>2.166666627777778</v>
+        <v>-0.3</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4420192159037534</v>
+        <v>2.183263424296428</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>2.166666627777778</v>
+        <v>-0.3</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4420192007475526</v>
+        <v>2.183263409140228</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>2.166666627777778</v>
+        <v>-0.3</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4420193068409581</v>
+        <v>2.183263515233633</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>2.166666627777778</v>
+        <v>-0.3</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4420190340293438</v>
+        <v>2.183263242422019</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.166666627777778</v>
+        <v>-0.3</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4420191325446491</v>
+        <v>2.183263340937324</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>2.166666627777778</v>
+        <v>-0.3</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4420192841066569</v>
+        <v>2.183263492499332</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>2.166666627777778</v>
+        <v>-0.3</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4420192992628578</v>
+        <v>2.183263507655533</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>2.166666627777778</v>
+        <v>-0.3</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4420192765285566</v>
+        <v>2.183263484921231</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>2.166666627777778</v>
+        <v>-0.3</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4420193598876609</v>
+        <v>2.183263568280336</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.3</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4420194584029661</v>
+        <v>2.183263666795641</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.3</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4420192916847575</v>
+        <v>2.183263500077433</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.3</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4420192765285566</v>
+        <v>2.183263484921231</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4420192462161551</v>
+        <v>2.18326345460883</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4420192310599543</v>
+        <v>2.183263439452629</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.3</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4420192689504563</v>
+        <v>2.183263477343131</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.566666627777779</v>
+        <v>-0.3</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4420192841066569</v>
+        <v>2.183263492499332</v>
       </c>
     </row>
     <row r="126">
@@ -101103,7 +101103,7 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-3.970767248321669e-06</v>
+        <v>-3.857095742388521e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.3</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4420192765285566</v>
+        <v>2.183263484921231</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-mamba2_repeat_1_000007.xlsx
+++ b/out/LSTM-mamba2_repeat_1_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.09333333222222223</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.566666627777779</v>
+        <v>0.5733333205555557</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.166666627777778</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>2.166666627777778</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>2.166666627777778</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.166666627777778</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>2.166666627777778</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>2.166666627777778</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>2.166666627777778</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.166666627777778</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.566666627777779</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.566666627777779</v>
+        <v>0.5733333205555557</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.09333333222222223</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,17 +31942,17 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC39" t="n">
-        <v>0</v>
+        <v>-4.204383576591499e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,21 +32733,21 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0</v>
+        <v>0.4847033316160194</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA40" t="n">
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC40" t="n">
-        <v>-6.544820638163947e-05</v>
+        <v>0.9701559271089146</v>
       </c>
     </row>
     <row r="41">
@@ -33528,21 +33528,21 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>-0.08439480559912851</v>
+        <v>0.07268342672862528</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC41" t="n">
-        <v>-0.08446025380551012</v>
+        <v>0.6301689104081777</v>
       </c>
     </row>
     <row r="42">
@@ -34323,21 +34323,21 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0</v>
+        <v>0.09087787632774534</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA42" t="n">
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC42" t="n">
-        <v>-0.0845195349753116</v>
+        <v>0.7392528925465015</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.09896576060908549</v>
+        <v>0.1302730047364316</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC43" t="n">
-        <v>0.1136497132289545</v>
+        <v>0.9089725242863712</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.136155436148725</v>
+        <v>0.1393666586790904</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.2870067489827375</v>
+        <v>1.0574422245036</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.1591724543333937</v>
+        <v>0.1476998298021145</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.4692093156517008</v>
+        <v>1.213487247913796</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.07118428547290268</v>
+        <v>0.06665418615384054</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.4522619758627245</v>
+        <v>1.198972908463701</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.03426610669047592</v>
+        <v>0.0321915685424732</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.4495476573862869</v>
+        <v>1.196648260635381</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.01624806723683932</v>
+        <v>0.01533798176126888</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.4477489483733648</v>
+        <v>1.195107433292252</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.004472507594134571</v>
+        <v>0.004540665218859847</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.4404296968309218</v>
+        <v>1.188838438451495</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.003091197288664339</v>
+        <v>0.003001784048697964</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.4421367540823403</v>
+        <v>1.190299678048884</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.001584137874602457</v>
+        <v>0.001533905803668403</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.4422126150571173</v>
+        <v>1.190363940108543</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0008103004465842412</v>
+        <v>0.0007822097914939123</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.4422480320039561</v>
+        <v>1.190393561171656</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0002889485289411763</v>
+        <v>0.0002909420026185476</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.442014038558902</v>
+        <v>1.190192388912688</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0001571842594622037</v>
+        <v>0.0001567011715426861</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.4420399776976137</v>
+        <v>1.190213927085576</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>7.264066268727065e-05</v>
+        <v>7.288353515471618e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.4420279255102805</v>
+        <v>1.190202890736951</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>4.460616585560791e-05</v>
+        <v>4.321380075431697e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.4420446442666803</v>
+        <v>1.190216398384154</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>2.155523189501682e-05</v>
+        <v>1.970485977965084e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.4420422451232253</v>
+        <v>1.190213596285759</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>7.395902747928427e-06</v>
+        <v>6.989117569422133e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.4420363490378794</v>
+        <v>1.190207823882263</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>3.158324102806951e-06</v>
+        <v>2.674878266576269e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.4420355440154751</v>
+        <v>1.190206459633018</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-7.922409131858519e-07</v>
+        <v>-1.503166167089948e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.4420296289786946</v>
+        <v>1.190200659683927</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.168604696895391e-06</v>
+        <v>-2.941261685029097e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.4420240808504736</v>
+        <v>1.190195111555706</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.001043275021943e-06</v>
+        <v>-3.887371769088796e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4420192462161551</v>
+        <v>1.190190276921388</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4420191022322476</v>
+        <v>1.19019013293748</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4420190794979462</v>
+        <v>1.190190110203179</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.442019397778163</v>
+        <v>1.190190428483395</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4420204890246198</v>
+        <v>1.190191519729853</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4420197994174839</v>
+        <v>1.190190830122717</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4420198297298856</v>
+        <v>1.190190860435118</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4420196402773754</v>
+        <v>1.190190670982608</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4420196933240784</v>
+        <v>1.190190724029311</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4420197463707812</v>
+        <v>1.190190777076014</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4420197084802792</v>
+        <v>1.190190739185512</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4420195796525725</v>
+        <v>1.190190610357805</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.442019435668665</v>
+        <v>1.190190466373898</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4420192765285566</v>
+        <v>1.190190307233789</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4420193295752595</v>
+        <v>1.190190360280492</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4420192765285566</v>
+        <v>1.190190307233789</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4420192765285566</v>
+        <v>1.190190307233789</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4420190946541471</v>
+        <v>1.19019012535938</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4420192613723558</v>
+        <v>1.190190292077588</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4420194584029661</v>
+        <v>1.190190489108199</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4420192992628578</v>
+        <v>1.190190329968091</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4420193371533598</v>
+        <v>1.190190367858592</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4420195341839699</v>
+        <v>1.190190564889203</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4420195114496688</v>
+        <v>1.190190542154902</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4420193598876609</v>
+        <v>1.190190390592894</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4420192841066569</v>
+        <v>1.19019031481189</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4420193826219621</v>
+        <v>1.190190413327195</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4420193902000624</v>
+        <v>1.190190420905295</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4420196554335763</v>
+        <v>1.190190686138809</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4420193598876609</v>
+        <v>1.190190390592894</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4420196023868737</v>
+        <v>1.190190633092106</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4420196857459781</v>
+        <v>1.19019071645121</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4420195190277693</v>
+        <v>1.190190549733002</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4420197084802792</v>
+        <v>1.190190739185512</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4420193598876609</v>
+        <v>1.190190390592894</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4420191552789502</v>
+        <v>1.190190185984183</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4420192689504563</v>
+        <v>1.190190299655689</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4420192841066569</v>
+        <v>1.19019031481189</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4420190491855447</v>
+        <v>1.190190079890777</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4420191098103479</v>
+        <v>1.19019014051558</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4420189809826412</v>
+        <v>1.190190011687874</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4420191173884482</v>
+        <v>1.190190148093681</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4420192916847575</v>
+        <v>1.19019032238999</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.442019435668665</v>
+        <v>1.190190466373898</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4420192689504563</v>
+        <v>1.190190299655689</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4420192613723558</v>
+        <v>1.190190292077588</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000004</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4420189734045407</v>
+        <v>1.190190004109773</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.349999978125</v>
+        <v>0.1066666677777778</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4420189885607415</v>
+        <v>1.190190019265974</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>2.166666627777778</v>
+        <v>0.7733333205555558</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4420192159037534</v>
+        <v>1.190190246608986</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>2.166666627777778</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4420192007475526</v>
+        <v>1.190190231452785</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>2.166666627777778</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4420193068409581</v>
+        <v>1.190190337546191</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>2.166666627777778</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4420190340293438</v>
+        <v>1.190190064734577</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.166666627777778</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4420191325446491</v>
+        <v>1.190190163249882</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>2.166666627777778</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4420192841066569</v>
+        <v>1.19019031481189</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>2.166666627777778</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4420192992628578</v>
+        <v>1.190190329968091</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>2.166666627777778</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4420192765285566</v>
+        <v>1.190190307233789</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>2.166666627777778</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4420193598876609</v>
+        <v>1.190190390592894</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.566666627777779</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4420194584029661</v>
+        <v>1.190190489108199</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.566666627777779</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4420192916847575</v>
+        <v>1.19019032238999</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.566666627777779</v>
+        <v>0.5733333205555557</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4420192765285566</v>
+        <v>1.190190307233789</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.09333333222222231</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4420192462161551</v>
+        <v>1.190190276921388</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.09333333222222231</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4420192310599543</v>
+        <v>1.190190261765187</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.566666627777779</v>
+        <v>0.5733333205555557</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4420192689504563</v>
+        <v>1.190190299655689</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.566666627777779</v>
+        <v>0.5733333205555557</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4420192841066569</v>
+        <v>1.19019031481189</v>
       </c>
     </row>
     <row r="126">
@@ -101103,7 +101103,7 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-3.970767248321669e-06</v>
+        <v>-3.857095742388521e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.349999978125</v>
+        <v>0.2399999941666666</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4420192765285566</v>
+        <v>1.190190307233789</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-mamba2_repeat_1_000007.xlsx
+++ b/out/LSTM-mamba2_repeat_1_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.2830961048603058</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-1.28</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.1487436890602112</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.8599999999999997</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.0457623079419136</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.02597292512655258</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.09333333222222223</v>
+        <v>-0.16</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.002135338261723518</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.5733333205555557</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.0142085924744606</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.439999973333334</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.01669514551758766</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.439999973333334</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.01055539958178997</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.439999973333334</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.007915548980236053</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.439999973333334</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.005183404311537743</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.439999973333334</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.007909687235951424</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.439999973333334</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.009579768404364586</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.439999973333334</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.01067290082573891</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.439999973333334</v>
+        <v>-0.16</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.007651668041944504</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.439999973333334</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.003523211926221848</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.239999973333334</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.009163279086351395</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.239999973333334</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.0140673890709877</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.239999973333334</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.01410116627812386</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.239999973333334</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.01090727746486664</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.239999973333334</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.0141238309442997</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.239999973333334</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.01251803338527679</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.239999973333334</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.007436767220497131</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.239999973333334</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.009707801043987274</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.239999973333334</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.01640341058373451</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.239999973333334</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.02006712555885315</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.239999973333334</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.01961952075362206</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.239999973333334</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.01899132877588272</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.239999973333334</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.01642413437366486</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.239999973333334</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.007656995207071304</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.239999973333334</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.01266185939311981</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.239999973333334</v>
+        <v>-0.16</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.01465624570846558</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.239999973333334</v>
+        <v>-0.3</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.01365163177251816</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.239999973333334</v>
+        <v>-0.3</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.01387811079621315</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.239999973333334</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.01412484049797058</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.239999973333334</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.008521024137735367</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.5733333205555557</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.01191462948918343</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.09333333222222223</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.006342712789773941</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.004003395326435566</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
-        <v>-4.204383576591499e-05</v>
+        <v>-2.374188724905252e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0.4847033316160194</v>
+        <v>0.2737088198054883</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.01412838697433472</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
-        <v>0.9701559271089146</v>
+        <v>0.5478408956059538</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.07268342672862528</v>
+        <v>0.04104385848346254</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.02203603647649288</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
-        <v>0.6301689104081777</v>
+        <v>0.3558523317891599</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.09087787632774534</v>
+        <v>0.05131817791221478</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.0231616385281086</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
-        <v>0.7392528925465015</v>
+        <v>0.4174514153839927</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.1302730047364316</v>
+        <v>0.07356452734066871</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.03406024351716042</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
-        <v>0.9089725242863712</v>
+        <v>0.5132911398550274</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1393666586790904</v>
+        <v>0.07869912454886685</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.03718223422765732</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>1.0574422245036</v>
+        <v>0.5971310431035201</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.1476998298021145</v>
+        <v>0.08340520947857311</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.04396466910839081</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.213487247913796</v>
+        <v>0.6852490732180814</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.06665418615384054</v>
+        <v>0.03763988566566401</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.05071377009153366</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>1.198972908463701</v>
+        <v>0.6770528489537041</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.0321915685424732</v>
+        <v>0.01817834438752623</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.1039038673043251</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>1.196648260635381</v>
+        <v>0.675740137249484</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.01533798176126888</v>
+        <v>0.008659070097109081</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.1316689550876617</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>1.195107433292252</v>
+        <v>0.6748678667302993</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.004540665218859847</v>
+        <v>0.002562109210075422</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.151781439781189</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.188838438451495</v>
+        <v>0.6713256341973552</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.003001784048697964</v>
+        <v>0.001692564140025768</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.1496171653270721</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.190299678048884</v>
+        <v>0.6721485431140889</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.001533905803668403</v>
+        <v>0.0008638323686951406</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.137841135263443</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.190363940108543</v>
+        <v>0.6721826568485764</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0007822097914939123</v>
+        <v>0.0004399446647574287</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.1226074621081352</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.190393561171656</v>
+        <v>0.6721972124257304</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0002909420026185476</v>
+        <v>0.00016227156669744</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.1022303551435471</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.190192388912688</v>
+        <v>0.6720814738013171</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0001567011715426861</v>
+        <v>8.575065749844627e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.08365552872419357</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.190213927085576</v>
+        <v>0.6720914358767597</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>7.288353515471618e-05</v>
+        <v>3.871014728070806e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.0622192956507206</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.190202890736951</v>
+        <v>0.6720830178176805</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>4.321380075431697e-05</v>
+        <v>2.255074328818113e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.04980101808905602</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.190216398384154</v>
+        <v>0.6720885936160828</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>1.970485977965084e-05</v>
+        <v>9.411168204796322e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.03634971380233765</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.190213596285759</v>
+        <v>0.6720848492020007</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>6.989117569422133e-06</v>
+        <v>1.993651915496244e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.04330342262983322</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.190207823882263</v>
+        <v>0.6720794163155286</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>2.674878266576269e-06</v>
+        <v>-1.162560866711865e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.05524372309446335</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.190206459633018</v>
+        <v>0.6720763743857638</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-1.503166167089948e-06</v>
+        <v>-2.668777444726632e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.07206541299819946</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.190200659683927</v>
+        <v>0.6720709168673735</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-2.941261685029097e-06</v>
+        <v>-3.970630842514548e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.07720810174942017</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.190195111555706</v>
+        <v>0.6720656428032632</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-3.887371769088796e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.08099665492773056</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.190190276921388</v>
+        <v>0.6720657261623675</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.07739539444446564</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.19019013293748</v>
+        <v>0.67206558217846</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.06605221331119537</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.190190110203179</v>
+        <v>0.6720655594441586</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.05372108891606331</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.190190428483395</v>
+        <v>0.6720658777243753</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.01195640861988068</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.190191519729853</v>
+        <v>0.6720669689708322</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.07220500707626343</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.16</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.190190830122717</v>
+        <v>0.6720662793636962</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.1640874445438385</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.190190860435118</v>
+        <v>0.6720663096760979</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.2241076529026031</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.190190670982608</v>
+        <v>0.6720661202235878</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.239557683467865</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.190190724029311</v>
+        <v>0.6720661732702907</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.2281157970428467</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.190190777076014</v>
+        <v>0.6720662263169936</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.1947884559631348</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.190190739185512</v>
+        <v>0.6720661884264916</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.1608122289180756</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.190190610357805</v>
+        <v>0.6720660595987848</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.1299655437469482</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.190190466373898</v>
+        <v>0.6720659156148774</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.09917378425598145</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.190190307233789</v>
+        <v>0.672065756474769</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.07621917128562927</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.190190360280492</v>
+        <v>0.6720658095214719</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.05268396064639091</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.190190307233789</v>
+        <v>0.672065756474769</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.0456082858145237</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.190190307233789</v>
+        <v>0.672065756474769</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.03402839601039886</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.19019012535938</v>
+        <v>0.6720655746003594</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.02518536150455475</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.190190292077588</v>
+        <v>0.6720657413185681</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.0234193429350853</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.190190489108199</v>
+        <v>0.6720659383491785</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.01816295459866524</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.190190329968091</v>
+        <v>0.6720657792090702</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.01926830038428307</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.190190367858592</v>
+        <v>0.6720658170995721</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.02539227902889252</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.190190564889203</v>
+        <v>0.6720660141301823</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.03053918108344078</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.190190542154902</v>
+        <v>0.6720659913958812</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.03107376769185066</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.16</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.190190390592894</v>
+        <v>0.6720658398338734</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.02741807326674461</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.3</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.19019031481189</v>
+        <v>0.6720657640528693</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.02637837082147598</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.3</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.190190413327195</v>
+        <v>0.6720658625681745</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.02905824407935143</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.16</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.190190420905295</v>
+        <v>0.6720658701462748</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.0334574319422245</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.190190686138809</v>
+        <v>0.6720661353797887</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.027126494795084</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.190190390592894</v>
+        <v>0.6720658398338734</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.02524547651410103</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.190190633092106</v>
+        <v>0.6720660823330861</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.03170566260814667</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.19019071645121</v>
+        <v>0.6720661656921904</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.03885261714458466</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.190190549733002</v>
+        <v>0.6720659989739817</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.05620529875159264</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.3</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.190190739185512</v>
+        <v>0.6720661884264916</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.06525808572769165</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.3</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.190190390592894</v>
+        <v>0.6720658398338734</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.06433817744255066</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.3</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.190190185984183</v>
+        <v>0.6720656352251626</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.05497680604457855</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.16</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.190190299655689</v>
+        <v>0.6720657488966687</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.05477921664714813</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.7599999850000004</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.19019031481189</v>
+        <v>0.6720657640528693</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.0432233065366745</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.190190079890777</v>
+        <v>0.6720655291317571</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.03309132158756256</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.19019014051558</v>
+        <v>0.6720655897565603</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.01734090596437454</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.190190011687874</v>
+        <v>0.6720654609288536</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.01858445629477501</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.190190148093681</v>
+        <v>0.6720655973346605</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.009186871349811554</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.19019032238999</v>
+        <v>0.6720657716309698</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.00783982127904892</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.190190466373898</v>
+        <v>0.6720659156148774</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.01112861931324005</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.190190299655689</v>
+        <v>0.6720657488966687</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.02247009053826332</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.190190292077588</v>
+        <v>0.6720657413185681</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.01719097048044205</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.7599999850000004</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.190190004109773</v>
+        <v>0.6720654533507531</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.003589833155274391</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.1066666677777778</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.190190019265974</v>
+        <v>0.6720654685069539</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.001854471862316132</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.7733333205555558</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.190190246608986</v>
+        <v>0.6720656958499658</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.004243016242980957</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.439999973333334</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.190190231452785</v>
+        <v>0.6720656806937649</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.001262661069631577</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.439999973333334</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.190190337546191</v>
+        <v>0.6720657867871704</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.005147136747837067</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.439999973333334</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.190190064734577</v>
+        <v>0.6720655139755563</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.009856164455413818</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.439999973333334</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.190190163249882</v>
+        <v>0.6720656124908615</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.009277584031224251</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.439999973333334</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.19019031481189</v>
+        <v>0.6720657640528693</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.009325873106718063</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.439999973333334</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.190190329968091</v>
+        <v>0.6720657792090702</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.007870962843298912</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.439999973333334</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.190190307233789</v>
+        <v>0.672065756474769</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.005426874384284019</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.439999973333334</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.190190390592894</v>
+        <v>0.6720658398338734</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.00575738400220871</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.439999973333334</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.190190489108199</v>
+        <v>0.6720659383491785</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.003315296024084091</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.239999973333334</v>
+        <v>-0.16</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.19019032238999</v>
+        <v>0.6720657716309698</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.0009274333715438843</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.5733333205555557</v>
+        <v>-0.3</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.190190307233789</v>
+        <v>0.672065756474769</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.00175994448363781</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.09333333222222231</v>
+        <v>-0.3</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.190190276921388</v>
+        <v>0.6720657261623675</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.001018218696117401</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.09333333222222231</v>
+        <v>-0.3</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.190190261765187</v>
+        <v>0.6720657110061666</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.003004537895321846</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.5733333205555557</v>
+        <v>-0.3</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.190190299655689</v>
+        <v>0.6720657488966687</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.001463074237108231</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.5733333205555557</v>
+        <v>-0.3</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.19019031481189</v>
+        <v>0.6720657640528693</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.005107983946800232</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.2399999941666666</v>
+        <v>-0.3</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.190190307233789</v>
+        <v>0.672065756474769</v>
       </c>
     </row>
   </sheetData>
